--- a/reports/2026-10-13_Collateral_Report.xlsx
+++ b/reports/2026-10-13_Collateral_Report.xlsx
@@ -35,7 +35,7 @@
     <t>Overall Cover</t>
   </si>
   <si>
-    <t>3.30x</t>
+    <t>3.33x</t>
   </si>
   <si>
     <t>Security Monitoring Details</t>
@@ -483,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>762500000</v>
+        <v>760000000</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -491,7 +491,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2513191242</v>
+        <v>2527463156</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -565,19 +565,19 @@
         <v>19</v>
       </c>
       <c r="D4" s="3">
-        <v>567.15</v>
+        <v>571</v>
       </c>
       <c r="E4" s="4">
         <v>2066600</v>
       </c>
       <c r="F4" s="3">
-        <v>762500000</v>
+        <v>760000000</v>
       </c>
       <c r="G4" s="3">
-        <v>1172072190</v>
+        <v>1180028600</v>
       </c>
       <c r="H4" s="5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
@@ -597,19 +597,19 @@
         <v>21</v>
       </c>
       <c r="D5" s="3">
-        <v>492.66</v>
+        <v>494.98</v>
       </c>
       <c r="E5" s="4">
         <v>2722200</v>
       </c>
       <c r="F5" s="3">
-        <v>762500000</v>
+        <v>760000000</v>
       </c>
       <c r="G5" s="3">
-        <v>1341119052</v>
+        <v>1347434556</v>
       </c>
       <c r="H5" s="5">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
